--- a/experiments/prompt-tuning/hc+ft/Results/Cardd_qwen_greedy/cardd_prompt03.xlsx
+++ b/experiments/prompt-tuning/hc+ft/Results/Cardd_qwen_greedy/cardd_prompt03.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UshariRanasinghe\Desktop\Projects\vlm-research\experiments\prompt-tuning\hc+ft\Results\Cardd_qwen_greedy\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24C1369-580B-48D5-A6E4-3E9DFBA1DE19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -109,8 +115,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +179,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -193,7 +207,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -231,7 +251,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -269,7 +295,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -307,7 +339,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -345,7 +383,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -383,7 +427,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -421,7 +471,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -459,7 +515,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -497,7 +559,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -535,7 +603,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -604,7 +678,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,9 +710,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -670,6 +762,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -845,11 +955,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:J12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>0</v>
       </c>
@@ -892,13 +1002,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>0.8049265146255493</v>
+        <v>0.80492651462554932</v>
       </c>
       <c r="G2">
-        <v>0.3333333333333334</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="H2">
-        <v>2.107284012381813</v>
+        <v>2.1072840123818128</v>
       </c>
       <c r="I2">
         <v>7104.80078125</v>
@@ -907,7 +1017,7 @@
         <v>18.95299506187439</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -921,13 +1031,13 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.8121694922447205</v>
+        <v>0.81216949224472046</v>
       </c>
       <c r="G3">
         <v>0.2857142857142857</v>
       </c>
       <c r="H3">
-        <v>3.074926922583952</v>
+        <v>3.0749269225839519</v>
       </c>
       <c r="I3">
         <v>7112.92578125</v>
@@ -936,7 +1046,7 @@
         <v>5.345069408416748</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -950,22 +1060,22 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.8274933099746704</v>
+        <v>0.82749330997467041</v>
       </c>
       <c r="G4">
-        <v>0.2702702702702703</v>
+        <v>0.27027027027027029</v>
       </c>
       <c r="H4">
-        <v>2.980880985154481</v>
+        <v>2.9808809851544811</v>
       </c>
       <c r="I4">
         <v>7112.92578125</v>
       </c>
       <c r="J4">
-        <v>3.280848979949951</v>
+        <v>3.2808489799499512</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -979,22 +1089,22 @@
         <v>23</v>
       </c>
       <c r="F5">
-        <v>0.7662696838378906</v>
+        <v>0.76626968383789063</v>
       </c>
       <c r="G5">
         <v>0.2388059701492537</v>
       </c>
       <c r="H5">
-        <v>2.250172239609286</v>
+        <v>2.2501722396092858</v>
       </c>
       <c r="I5">
         <v>7142.08740234375</v>
       </c>
       <c r="J5">
-        <v>9.638797521591187</v>
+        <v>9.6387975215911865</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1008,10 +1118,10 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>0.4818779826164246</v>
+        <v>0.48187798261642462</v>
       </c>
       <c r="G6">
-        <v>0.0909090909090909</v>
+        <v>9.0909090909090898E-2</v>
       </c>
       <c r="H6">
         <v>1.328129471175177</v>
@@ -1023,7 +1133,7 @@
         <v>6.07454514503479</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1037,22 +1147,22 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0.8248132467269897</v>
+        <v>0.82481324672698975</v>
       </c>
       <c r="G7">
-        <v>0.2264150943396226</v>
+        <v>0.22641509433962259</v>
       </c>
       <c r="H7">
-        <v>2.078839732612902</v>
+        <v>2.0788397326129018</v>
       </c>
       <c r="I7">
         <v>7118.92578125</v>
       </c>
       <c r="J7">
-        <v>5.308939218521118</v>
+        <v>5.3089392185211182</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1066,7 +1176,7 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>0.7969112396240234</v>
+        <v>0.79691123962402344</v>
       </c>
       <c r="G8">
         <v>0.1481481481481482</v>
@@ -1078,10 +1188,10 @@
         <v>7118.92578125</v>
       </c>
       <c r="J8">
-        <v>3.792111396789551</v>
+        <v>3.7921113967895508</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1095,13 +1205,13 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>0.864628791809082</v>
+        <v>0.86462879180908203</v>
       </c>
       <c r="G9">
         <v>0.375</v>
       </c>
       <c r="H9">
-        <v>3.133122607308003</v>
+        <v>3.1331226073080032</v>
       </c>
       <c r="I9">
         <v>7111.1142578125</v>
@@ -1110,7 +1220,7 @@
         <v>3.967605352401733</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1124,7 +1234,7 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0.7963188886642456</v>
+        <v>0.79631888866424561</v>
       </c>
       <c r="G10">
         <v>0.1224489795918367</v>
@@ -1136,10 +1246,10 @@
         <v>7142.08740234375</v>
       </c>
       <c r="J10">
-        <v>4.011107444763184</v>
+        <v>4.0111074447631836</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1153,10 +1263,10 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.7328506708145142</v>
+        <v>0.73285067081451416</v>
       </c>
       <c r="G11">
-        <v>0.1772151898734177</v>
+        <v>0.17721518987341769</v>
       </c>
       <c r="H11">
         <v>2.740601054795782</v>
@@ -1165,7 +1275,29 @@
         <v>7142.08740234375</v>
       </c>
       <c r="J11">
-        <v>4.646591663360596</v>
+        <v>4.6465916633605957</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <f>AVERAGE(F3:F11)</f>
+        <v>0.767037034034729</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:J12" si="0">AVERAGE(G3:G11)</f>
+        <v>0.21499189211065842</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>2.3810153864553163</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>7124.4450412326387</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>5.1184017923143177</v>
       </c>
     </row>
   </sheetData>
